--- a/dev/ValueSet-occupational-classifications.xlsx
+++ b/dev/ValueSet-occupational-classifications.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T03:12:48+00:00</t>
+    <t>2026-03-18T09:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-occupational-classifications.xlsx
+++ b/dev/ValueSet-occupational-classifications.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T09:54:13+00:00</t>
+    <t>2026-03-23T13:24:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-occupational-classifications.xlsx
+++ b/dev/ValueSet-occupational-classifications.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:24:52+00:00</t>
+    <t>2026-03-25T02:48:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-occupational-classifications.xlsx
+++ b/dev/ValueSet-occupational-classifications.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T02:48:03+00:00</t>
+    <t>2026-03-25T03:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-occupational-classifications.xlsx
+++ b/dev/ValueSet-occupational-classifications.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:05:28+00:00</t>
+    <t>2026-03-25T03:10:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-occupational-classifications.xlsx
+++ b/dev/ValueSet-occupational-classifications.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:10:05+00:00</t>
+    <t>2026-03-25T03:15:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-occupational-classifications.xlsx
+++ b/dev/ValueSet-occupational-classifications.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:15:34+00:00</t>
+    <t>2026-03-25T03:26:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-occupational-classifications.xlsx
+++ b/dev/ValueSet-occupational-classifications.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:26:10+00:00</t>
+    <t>2026-03-25T03:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-occupational-classifications.xlsx
+++ b/dev/ValueSet-occupational-classifications.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:31:02+00:00</t>
+    <t>2026-03-25T03:34:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-occupational-classifications.xlsx
+++ b/dev/ValueSet-occupational-classifications.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:34:45+00:00</t>
+    <t>2026-03-25T03:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-occupational-classifications.xlsx
+++ b/dev/ValueSet-occupational-classifications.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:48:45+00:00</t>
+    <t>2026-03-25T03:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-occupational-classifications.xlsx
+++ b/dev/ValueSet-occupational-classifications.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:54:03+00:00</t>
+    <t>2026-04-01T03:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-occupational-classifications.xlsx
+++ b/dev/ValueSet-occupational-classifications.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -59,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:21:07+00:00</t>
+    <t>2026-04-01T03:34:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -77,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Philippines</t>
+    <t>Philippines (the)</t>
   </si>
   <si>
     <t>Description</t>
@@ -96,6 +97,21 @@
   </si>
   <si>
     <t>BooleanType[null]</t>
+  </si>
+  <si>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>https://psa.gov.ph/classification/psoc/unit</t>
   </si>
 </sst>
 </file>
@@ -355,4 +371,44 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/dev/ValueSet-occupational-classifications.xlsx
+++ b/dev/ValueSet-occupational-classifications.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:34:09+00:00</t>
+    <t>2026-04-01T03:44:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-occupational-classifications.xlsx
+++ b/dev/ValueSet-occupational-classifications.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:44:59+00:00</t>
+    <t>2026-04-06T07:53:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-occupational-classifications.xlsx
+++ b/dev/ValueSet-occupational-classifications.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-06T07:53:57+00:00</t>
+    <t>2026-04-08T04:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-occupational-classifications.xlsx
+++ b/dev/ValueSet-occupational-classifications.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:01:15+00:00</t>
+    <t>2026-04-13T08:21:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
